--- a/data/trans_dic/P22$ss-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P22$ss-Edad-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, al menor, es beneficiaria de Seguridad Social</t>
+          <t>Población que, al menos, es beneficiaria de la Seguridad Social (tasa de respuesta: 99,93%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>94,84; 97,93</t>
+          <t>94,79; 98,02</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>93,84; 97,77</t>
+          <t>93,78; 97,78</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>94,62; 98,01</t>
+          <t>94,34; 98,01</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>93,49; 99,2</t>
+          <t>93,01; 99,16</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>91,36; 95,67</t>
+          <t>91,5; 96,11</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,1; 98,43</t>
+          <t>95,07; 98,44</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>95,07; 98,48</t>
+          <t>95,04; 98,35</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>93,39; 99,65</t>
+          <t>93,35; 99,66</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>93,86; 96,64</t>
+          <t>93,79; 96,57</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>95,08; 97,68</t>
+          <t>95,0; 97,62</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>95,64; 97,93</t>
+          <t>95,42; 97,88</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>94,9; 98,96</t>
+          <t>94,89; 98,89</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>94,3; 97,4</t>
+          <t>94,38; 97,46</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>93,49; 96,96</t>
+          <t>93,52; 97,04</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>93,89; 97,25</t>
+          <t>93,91; 97,32</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>93,65; 98,41</t>
+          <t>93,93; 98,52</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>93,01; 96,58</t>
+          <t>92,94; 96,56</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>94,07; 97,38</t>
+          <t>93,93; 97,42</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>94,4; 97,64</t>
+          <t>94,26; 97,64</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>96,36; 99,23</t>
+          <t>96,14; 99,19</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>94,26; 96,64</t>
+          <t>94,37; 96,63</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>94,49; 96,88</t>
+          <t>94,17; 96,76</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>94,92; 97,18</t>
+          <t>94,67; 97,1</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>96,06; 98,63</t>
+          <t>95,96; 98,53</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>93,76; 97,22</t>
+          <t>93,79; 97,22</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>92,38; 96,16</t>
+          <t>92,56; 96,36</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>91,52; 95,46</t>
+          <t>91,51; 95,51</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>94,47; 97,82</t>
+          <t>94,48; 97,93</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>94,2; 97,4</t>
+          <t>94,14; 97,34</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>94,62; 97,76</t>
+          <t>94,65; 97,84</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>93,2; 96,75</t>
+          <t>93,17; 96,69</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>94,97; 97,58</t>
+          <t>95,06; 97,67</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>94,63; 96,96</t>
+          <t>94,69; 96,97</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>94,1; 96,68</t>
+          <t>94,34; 96,74</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>92,91; 95,59</t>
+          <t>92,88; 95,62</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>95,35; 97,51</t>
+          <t>95,4; 97,47</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>89,91; 94,74</t>
+          <t>90,17; 95,06</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>92,01; 96,59</t>
+          <t>92,26; 96,79</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>92,26; 96,27</t>
+          <t>92,45; 96,25</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>94,97; 98,74</t>
+          <t>94,89; 98,73</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>93,56; 97,29</t>
+          <t>93,59; 97,3</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>91,74; 95,93</t>
+          <t>91,76; 96,05</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>94,18; 97,51</t>
+          <t>94,29; 97,39</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>95,45; 97,58</t>
+          <t>95,43; 97,71</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>92,68; 95,69</t>
+          <t>92,61; 95,69</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>92,66; 95,81</t>
+          <t>92,65; 95,86</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>93,97; 96,52</t>
+          <t>93,64; 96,47</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>95,74; 98,03</t>
+          <t>95,71; 98,13</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>94,5; 98,3</t>
+          <t>94,84; 98,27</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>91,53; 96,55</t>
+          <t>91,82; 96,62</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>91,36; 96,01</t>
+          <t>91,37; 95,88</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>95,56; 98,09</t>
+          <t>95,31; 98,07</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>90,27; 95,58</t>
+          <t>90,58; 95,7</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>94,04; 98,07</t>
+          <t>94,48; 98,24</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>94,79; 98,44</t>
+          <t>94,64; 98,44</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>95,13; 97,59</t>
+          <t>94,96; 97,48</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>93,55; 96,46</t>
+          <t>93,47; 96,5</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>93,84; 96,94</t>
+          <t>93,76; 96,95</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>93,91; 96,72</t>
+          <t>93,89; 96,76</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>95,71; 97,5</t>
+          <t>95,65; 97,48</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>92,79; 97,53</t>
+          <t>92,51; 97,57</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>90,48; 96,89</t>
+          <t>90,75; 96,65</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>93,5; 97,95</t>
+          <t>93,9; 97,89</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>92,49; 96,2</t>
+          <t>92,38; 96,32</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>93,11; 97,69</t>
+          <t>93,58; 97,71</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>95,97; 99,22</t>
+          <t>96,32; 99,22</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>93,26; 97,87</t>
+          <t>93,28; 97,76</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>95,27; 99,11</t>
+          <t>95,17; 98,78</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>93,99; 97,06</t>
+          <t>93,99; 97,12</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>94,27; 97,71</t>
+          <t>94,27; 97,83</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>94,19; 97,4</t>
+          <t>94,45; 97,41</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>94,74; 98,09</t>
+          <t>94,73; 98,07</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>93,4; 98,83</t>
+          <t>93,7; 98,81</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>95,33; 99,21</t>
+          <t>95,4; 99,19</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>95,29; 98,77</t>
+          <t>95,27; 99,07</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>93,9; 97,69</t>
+          <t>94,01; 97,58</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>96,58; 99,64</t>
+          <t>96,6; 99,64</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>94,64; 98,73</t>
+          <t>94,8; 98,87</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,26; 99,7</t>
+          <t>97,76; 99,7</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>96,04; 98,43</t>
+          <t>96,03; 98,34</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>96,39; 99,07</t>
+          <t>96,27; 99,01</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>95,83; 98,65</t>
+          <t>95,95; 98,71</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>97,19; 99,21</t>
+          <t>97,21; 99,2</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>95,62; 97,66</t>
+          <t>95,76; 97,82</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>94,93; 96,41</t>
+          <t>95,02; 96,43</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>94,31; 95,94</t>
+          <t>94,45; 96,02</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>94,27; 95,92</t>
+          <t>94,34; 95,85</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>95,78; 97,37</t>
+          <t>95,77; 97,41</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>94,72; 96,16</t>
+          <t>94,67; 96,12</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>95,61; 97,01</t>
+          <t>95,6; 97,05</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>95,87; 97,12</t>
+          <t>95,75; 97,03</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>96,47; 97,7</t>
+          <t>96,53; 97,64</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>95,06; 96,09</t>
+          <t>95,01; 96,03</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>95,3; 96,31</t>
+          <t>95,28; 96,34</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>95,25; 96,29</t>
+          <t>95,35; 96,29</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>96,34; 97,32</t>
+          <t>96,37; 97,39</t>
         </is>
       </c>
     </row>
@@ -1810,7 +1810,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, al menor, es beneficiaria de Seguridad Social</t>
+          <t>Población que, al menos, es beneficiaria de la Seguridad Social (tasa de respuesta: 99,93%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2068,62 +2068,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>467667; 482935</t>
+          <t>467434; 483361</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>425232; 443063</t>
+          <t>425000; 443111</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>395162; 409308</t>
+          <t>393958; 409300</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>373932; 396769</t>
+          <t>372043; 396629</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>427084; 447266</t>
+          <t>427739; 449314</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>409163; 423491</t>
+          <t>409033; 423518</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>376263; 389758</t>
+          <t>376112; 389230</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>292512; 312091</t>
+          <t>292386; 312125</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>901673; 928339</t>
+          <t>900975; 927662</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>839914; 862916</t>
+          <t>839252; 862342</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>777926; 796497</t>
+          <t>776089; 796133</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>676840; 705770</t>
+          <t>676764; 705302</t>
         </is>
       </c>
     </row>
@@ -2276,62 +2276,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>691227; 713957</t>
+          <t>691825; 714344</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>642349; 666216</t>
+          <t>642583; 666748</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>554444; 574273</t>
+          <t>554535; 574689</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>396662; 416817</t>
+          <t>397836; 417279</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>581790; 604111</t>
+          <t>581318; 603983</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>574073; 594240</t>
+          <t>573214; 594489</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>530227; 548448</t>
+          <t>529472; 548458</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>492741; 507409</t>
+          <t>491595; 507206</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1280457; 1312874</t>
+          <t>1281939; 1312651</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1225907; 1256919</t>
+          <t>1221757; 1255304</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1093630; 1119694</t>
+          <t>1090719; 1118736</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>898013; 922127</t>
+          <t>897087; 921123</t>
         </is>
       </c>
     </row>
@@ -2484,62 +2484,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>598810; 620901</t>
+          <t>598989; 620899</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>629934; 655683</t>
+          <t>631133; 657016</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>611529; 637797</t>
+          <t>611466; 638130</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>506654; 524666</t>
+          <t>506747; 525219</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>649730; 671798</t>
+          <t>649304; 671383</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>672591; 694956</t>
+          <t>672812; 695496</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>616425; 639907</t>
+          <t>616197; 639510</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>515179; 529344</t>
+          <t>515668; 529853</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1257085; 1288078</t>
+          <t>1257909; 1288203</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1310491; 1346413</t>
+          <t>1313951; 1347252</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>1235296; 1270891</t>
+          <t>1234910; 1271269</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>1028689; 1051903</t>
+          <t>1029178; 1051546</t>
         </is>
       </c>
     </row>
@@ -2692,62 +2692,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>465730; 490753</t>
+          <t>467105; 492404</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>565482; 593648</t>
+          <t>567032; 594886</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>596048; 621977</t>
+          <t>597303; 621798</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>843137; 876595</t>
+          <t>842455; 876497</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>481341; 500501</t>
+          <t>481486; 500595</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>565289; 591122</t>
+          <t>565426; 591845</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>610402; 631949</t>
+          <t>611117; 631167</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>680479; 695624</t>
+          <t>680291; 696580</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>956942; 987983</t>
+          <t>956127; 987925</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1140501; 1179203</t>
+          <t>1140347; 1179824</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1216077; 1249051</t>
+          <t>1211816; 1248406</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>1532450; 1569169</t>
+          <t>1531924; 1570703</t>
         </is>
       </c>
     </row>
@@ -2900,62 +2900,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>365442; 380136</t>
+          <t>366749; 380030</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>393044; 414624</t>
+          <t>394309; 414932</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>434655; 456816</t>
+          <t>434706; 456192</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>536292; 550507</t>
+          <t>534930; 550421</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>363915; 385313</t>
+          <t>365158; 385792</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>421090; 439145</t>
+          <t>423078; 439920</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>470970; 489085</t>
+          <t>470197; 489088</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>519019; 532397</t>
+          <t>518045; 531822</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>738890; 761896</t>
+          <t>738242; 762189</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>823150; 850358</t>
+          <t>822470; 850491</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>913417; 940773</t>
+          <t>913159; 941132</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>1059284; 1079102</t>
+          <t>1058682; 1078955</t>
         </is>
       </c>
     </row>
@@ -3108,62 +3108,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>271499; 285363</t>
+          <t>270668; 285465</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>280282; 300163</t>
+          <t>281141; 299423</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>312583; 327492</t>
+          <t>313942; 327286</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>340521; 354162</t>
+          <t>340118; 354609</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>319309; 335023</t>
+          <t>320932; 335075</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>339722; 351221</t>
+          <t>340984; 351246</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>350706; 368064</t>
+          <t>350781; 367637</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>579571; 602946</t>
+          <t>578998; 600958</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>597330; 616855</t>
+          <t>597327; 617220</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>625743; 648611</t>
+          <t>625762; 649360</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>669127; 691951</t>
+          <t>670972; 691967</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>925194; 957870</t>
+          <t>925027; 957654</t>
         </is>
       </c>
     </row>
@@ -3316,62 +3316,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>194320; 205601</t>
+          <t>194932; 205571</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>238191; 247875</t>
+          <t>238361; 247820</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>244898; 253845</t>
+          <t>244854; 254595</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>265508; 276240</t>
+          <t>265833; 275925</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>322488; 332712</t>
+          <t>322559; 332719</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>368136; 384056</t>
+          <t>368763; 384589</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>387965; 397686</t>
+          <t>389976; 397694</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>408982; 419140</t>
+          <t>408935; 418780</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>522372; 536922</t>
+          <t>521739; 536567</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>612209; 630191</t>
+          <t>612947; 630572</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>637471; 650704</t>
+          <t>637596; 650668</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>677586; 692022</t>
+          <t>678549; 693163</t>
         </is>
       </c>
     </row>
@@ -3524,62 +3524,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>3104184; 3152618</t>
+          <t>3107381; 3153465</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>3230977; 3286587</t>
+          <t>3235833; 3289280</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>3195178; 3251103</t>
+          <t>3197578; 3248907</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>3313703; 3368767</t>
+          <t>3313369; 3370348</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>3198770; 3247499</t>
+          <t>3197097; 3246151</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>3401956; 3451750</t>
+          <t>3401818; 3453496</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>3392445; 3436861</t>
+          <t>3388285; 3433545</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>3530609; 3575358</t>
+          <t>3532799; 3573450</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>6319080; 6387327</t>
+          <t>6315493; 6383131</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>6656193; 6726464</t>
+          <t>6654781; 6728209</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>6599057; 6671207</t>
+          <t>6606123; 6671010</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>6859215; 6928461</t>
+          <t>6861345; 6933410</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P22$ss-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P22$ss-Edad-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>97,27%</t>
+          <t>95,91%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>97,84%</t>
+          <t>98,14%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>97,52%</t>
+          <t>96,96%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>94,79; 98,02</t>
+          <t>94,76; 97,99</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>93,78; 97,78</t>
+          <t>93,56; 97,73</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>94,34; 98,01</t>
+          <t>94,56; 98,2</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>93,01; 99,16</t>
+          <t>92,04; 98,35</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>91,5; 96,11</t>
+          <t>91,5; 95,99</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,07; 98,44</t>
+          <t>94,92; 98,4</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>95,04; 98,35</t>
+          <t>95,24; 98,33</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>93,35; 99,66</t>
+          <t>94,48; 99,63</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>93,79; 96,57</t>
+          <t>93,81; 96,59</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>95,0; 97,62</t>
+          <t>95,12; 97,64</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>95,42; 97,88</t>
+          <t>95,45; 97,99</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>94,89; 98,89</t>
+          <t>94,33; 98,5</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>96,81%</t>
+          <t>96,61%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>98,14%</t>
+          <t>97,99%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>97,53%</t>
+          <t>97,32%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>94,38; 97,46</t>
+          <t>94,41; 97,41</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>93,52; 97,04</t>
+          <t>93,45; 97,13</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>93,91; 97,32</t>
+          <t>93,98; 97,26</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>93,93; 98,52</t>
+          <t>93,61; 98,42</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>92,94; 96,56</t>
+          <t>93,01; 96,68</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>93,93; 97,42</t>
+          <t>94,07; 97,57</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>94,26; 97,64</t>
+          <t>94,54; 97,56</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>96,14; 99,19</t>
+          <t>96,08; 99,16</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>94,37; 96,63</t>
+          <t>94,32; 96,65</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>94,17; 96,76</t>
+          <t>94,51; 96,88</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>94,67; 97,1</t>
+          <t>94,76; 97,08</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>95,96; 98,53</t>
+          <t>95,7; 98,4</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>96,47%</t>
+          <t>96,65%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>96,5%</t>
+          <t>96,71%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>96,48%</t>
+          <t>96,68%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>93,79; 97,22</t>
+          <t>93,73; 97,36</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>92,56; 96,36</t>
+          <t>92,31; 96,28</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>91,51; 95,51</t>
+          <t>91,43; 95,51</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>94,48; 97,93</t>
+          <t>94,89; 97,94</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>94,14; 97,34</t>
+          <t>94,32; 97,42</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>94,65; 97,84</t>
+          <t>94,71; 97,89</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>93,17; 96,69</t>
+          <t>93,12; 96,78</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>95,06; 97,67</t>
+          <t>95,18; 97,75</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>94,69; 96,97</t>
+          <t>94,55; 96,98</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>94,34; 96,74</t>
+          <t>94,2; 96,77</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>92,88; 95,62</t>
+          <t>92,91; 95,65</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>95,4; 97,47</t>
+          <t>95,52; 97,59</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>96,89%</t>
+          <t>95,9%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>96,69%</t>
+          <t>96,56%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>96,8%</t>
+          <t>96,24%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>90,17; 95,06</t>
+          <t>89,88; 94,84</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>92,26; 96,79</t>
+          <t>92,38; 96,63</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>92,45; 96,25</t>
+          <t>92,35; 96,28</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>94,89; 98,73</t>
+          <t>93,94; 97,31</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>93,59; 97,3</t>
+          <t>93,84; 97,35</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>91,76; 96,05</t>
+          <t>91,73; 95,99</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>94,29; 97,39</t>
+          <t>94,33; 97,3</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>95,43; 97,71</t>
+          <t>95,39; 97,4</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>92,61; 95,69</t>
+          <t>92,73; 95,58</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>92,65; 95,86</t>
+          <t>92,89; 95,84</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>93,64; 96,47</t>
+          <t>93,72; 96,38</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>95,71; 98,13</t>
+          <t>95,22; 97,13</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>96,94%</t>
+          <t>96,78%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>96,43%</t>
+          <t>96,5%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>96,69%</t>
+          <t>96,64%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>94,84; 98,27</t>
+          <t>94,94; 98,32</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>91,82; 96,62</t>
+          <t>91,57; 96,78</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>91,37; 95,88</t>
+          <t>91,54; 96,07</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>95,31; 98,07</t>
+          <t>95,14; 97,9</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>90,58; 95,7</t>
+          <t>90,35; 95,47</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>94,48; 98,24</t>
+          <t>93,91; 98,26</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>94,64; 98,44</t>
+          <t>94,65; 98,3</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>94,96; 97,48</t>
+          <t>95,19; 97,56</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>93,47; 96,5</t>
+          <t>93,49; 96,51</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>93,76; 96,95</t>
+          <t>93,66; 96,99</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>93,89; 96,76</t>
+          <t>93,88; 96,67</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>95,65; 97,48</t>
+          <t>95,66; 97,46</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>94,61%</t>
+          <t>94,81%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>97,21%</t>
+          <t>95,94%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>96,23%</t>
+          <t>95,4%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>92,51; 97,57</t>
+          <t>92,87; 97,46</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>90,75; 96,65</t>
+          <t>90,32; 96,83</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>93,9; 97,89</t>
+          <t>93,34; 98,02</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>92,38; 96,32</t>
+          <t>92,67; 96,4</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>93,58; 97,71</t>
+          <t>93,62; 97,63</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>96,32; 99,22</t>
+          <t>96,11; 99,22</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>93,28; 97,76</t>
+          <t>93,54; 97,89</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>95,17; 98,78</t>
+          <t>94,62; 97,28</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>93,99; 97,12</t>
+          <t>93,99; 97,04</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>94,27; 97,83</t>
+          <t>94,48; 97,74</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>94,45; 97,41</t>
+          <t>94,46; 97,4</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>94,73; 98,07</t>
+          <t>94,23; 96,46</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>96,14%</t>
+          <t>96,32%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>97,37%</t>
+          <t>97,31%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>96,88%</t>
+          <t>96,92%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>93,7; 98,81</t>
+          <t>93,67; 98,78</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>95,4; 99,19</t>
+          <t>95,57; 99,2</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>95,27; 99,07</t>
+          <t>95,37; 99,02</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>94,01; 97,58</t>
+          <t>93,94; 97,69</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>96,6; 99,64</t>
+          <t>96,59; 99,65</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>94,8; 98,87</t>
+          <t>94,75; 98,67</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,76; 99,7</t>
+          <t>97,42; 99,7</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>96,03; 98,34</t>
+          <t>95,9; 98,24</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>96,27; 99,01</t>
+          <t>96,13; 99,03</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>95,95; 98,71</t>
+          <t>95,91; 98,7</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>97,21; 99,2</t>
+          <t>97,12; 99,12</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>95,76; 97,82</t>
+          <t>95,81; 97,67</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>96,56%</t>
+          <t>96,19%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>97,09%</t>
+          <t>96,94%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>96,83%</t>
+          <t>96,58%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>95,02; 96,43</t>
+          <t>95,01; 96,37</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>94,45; 96,02</t>
+          <t>94,45; 96,01</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>94,34; 95,85</t>
+          <t>94,42; 95,91</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>95,77; 97,41</t>
+          <t>95,38; 96,83</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>94,67; 96,12</t>
+          <t>94,7; 96,15</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>95,6; 97,05</t>
+          <t>95,58; 96,97</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>95,75; 97,03</t>
+          <t>95,83; 97,05</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>96,53; 97,64</t>
+          <t>96,42; 97,37</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>95,01; 96,03</t>
+          <t>95,04; 96,13</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>95,28; 96,34</t>
+          <t>95,28; 96,32</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>95,35; 96,29</t>
+          <t>95,37; 96,31</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>96,37; 97,39</t>
+          <t>96,11; 96,97</t>
         </is>
       </c>
     </row>
@@ -2015,7 +2015,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>389076</t>
+          <t>391100</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2035,7 +2035,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>306440</t>
+          <t>355754</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2055,7 +2055,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>695516</t>
+          <t>746855</t>
         </is>
       </c>
     </row>
@@ -2068,62 +2068,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>467434; 483361</t>
+          <t>467283; 483234</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>425000; 443111</t>
+          <t>423983; 442882</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>393958; 409300</t>
+          <t>394880; 410105</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>372043; 396629</t>
+          <t>375320; 401057</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>427739; 449314</t>
+          <t>427739; 448765</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>409033; 423518</t>
+          <t>408394; 423355</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>376112; 389230</t>
+          <t>376915; 389141</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>292386; 312125</t>
+          <t>342489; 361184</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>900975; 927662</t>
+          <t>901186; 927916</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>839252; 862342</t>
+          <t>840315; 862547</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>776089; 796133</t>
+          <t>776394; 796994</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>676764; 705302</t>
+          <t>726599; 758743</t>
         </is>
       </c>
     </row>
@@ -2223,7 +2223,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>410022</t>
+          <t>460723</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2243,7 +2243,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>501810</t>
+          <t>489987</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2263,7 +2263,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>911832</t>
+          <t>950710</t>
         </is>
       </c>
     </row>
@@ -2276,62 +2276,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>691825; 714344</t>
+          <t>692014; 714021</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>642583; 666748</t>
+          <t>642095; 667341</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>554535; 574689</t>
+          <t>554920; 574294</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>397836; 417279</t>
+          <t>446423; 469349</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>581318; 603983</t>
+          <t>581749; 604720</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>573214; 594489</t>
+          <t>574096; 595411</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>529472; 548458</t>
+          <t>531016; 547977</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>491595; 507206</t>
+          <t>480410; 495839</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1281939; 1312651</t>
+          <t>1281329; 1312901</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1221757; 1255304</t>
+          <t>1226058; 1256862</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1090719; 1118736</t>
+          <t>1091832; 1118487</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>897087; 921123</t>
+          <t>934912; 961310</t>
         </is>
       </c>
     </row>
@@ -2431,7 +2431,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>517408</t>
+          <t>600029</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2451,7 +2451,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>523473</t>
+          <t>601641</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1040881</t>
+          <t>1201669</t>
         </is>
       </c>
     </row>
@@ -2484,62 +2484,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>598989; 620899</t>
+          <t>598638; 621839</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>631133; 657016</t>
+          <t>629424; 656477</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>611466; 638130</t>
+          <t>610911; 638170</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>506747; 525219</t>
+          <t>589095; 608063</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>649304; 671383</t>
+          <t>650595; 671919</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>672812; 695496</t>
+          <t>673220; 695821</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>616197; 639510</t>
+          <t>615863; 640083</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>515668; 529853</t>
+          <t>592149; 608138</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1257909; 1288203</t>
+          <t>1256063; 1288333</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1313951; 1347252</t>
+          <t>1311961; 1347781</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>1234910; 1271269</t>
+          <t>1235319; 1271742</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>1029178; 1051546</t>
+          <t>1187339; 1213054</t>
         </is>
       </c>
     </row>
@@ -2639,7 +2639,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>860148</t>
+          <t>671893</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2659,7 +2659,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>689312</t>
+          <t>711516</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2679,7 +2679,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>1549460</t>
+          <t>1383411</t>
         </is>
       </c>
     </row>
@@ -2692,62 +2692,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>467105; 492404</t>
+          <t>465583; 491295</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>567032; 594886</t>
+          <t>567803; 593899</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>597303; 621798</t>
+          <t>596632; 622042</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>842455; 876497</t>
+          <t>658134; 681783</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>481486; 500595</t>
+          <t>482776; 500814</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>565426; 591845</t>
+          <t>565242; 591476</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>611117; 631167</t>
+          <t>611373; 630577</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>680291; 696580</t>
+          <t>702946; 717707</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>956127; 987925</t>
+          <t>957434; 986880</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1140347; 1179824</t>
+          <t>1143266; 1179676</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1211816; 1248406</t>
+          <t>1212881; 1247265</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>1531924; 1570703</t>
+          <t>1368821; 1396319</t>
         </is>
       </c>
     </row>
@@ -2847,7 +2847,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>544032</t>
+          <t>589695</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2867,7 +2867,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>526095</t>
+          <t>586838</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2887,7 +2887,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>1070126</t>
+          <t>1176533</t>
         </is>
       </c>
     </row>
@@ -2900,62 +2900,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>366749; 380030</t>
+          <t>367141; 380220</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>394309; 414932</t>
+          <t>393234; 415587</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>434706; 456192</t>
+          <t>435540; 457101</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>534930; 550421</t>
+          <t>579726; 596561</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>365158; 385792</t>
+          <t>364239; 384874</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>423078; 439920</t>
+          <t>420546; 440020</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>470197; 489088</t>
+          <t>470275; 488387</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>518045; 531822</t>
+          <t>578902; 593282</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>738242; 762189</t>
+          <t>738438; 762307</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>822470; 850491</t>
+          <t>821640; 850851</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>913159; 941132</t>
+          <t>913095; 940215</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>1058682; 1078955</t>
+          <t>1164678; 1186558</t>
         </is>
       </c>
     </row>
@@ -3055,7 +3055,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>348339</t>
+          <t>385962</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3075,7 +3075,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>591421</t>
+          <t>421351</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3095,7 +3095,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>939759</t>
+          <t>807313</t>
         </is>
       </c>
     </row>
@@ -3108,62 +3108,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>270668; 285465</t>
+          <t>271717; 285162</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>281141; 299423</t>
+          <t>279802; 299966</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>313942; 327286</t>
+          <t>312052; 327696</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>340118; 354609</t>
+          <t>377229; 392433</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>320932; 335075</t>
+          <t>321040; 334797</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>340984; 351246</t>
+          <t>340243; 351218</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>350781; 367637</t>
+          <t>351762; 368118</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>578998; 600958</t>
+          <t>415553; 427206</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>597327; 617220</t>
+          <t>597313; 616723</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>625762; 649360</t>
+          <t>627116; 648762</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>670972; 691967</t>
+          <t>671026; 691913</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>925027; 957654</t>
+          <t>797456; 816251</t>
         </is>
       </c>
     </row>
@@ -3263,7 +3263,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>271841</t>
+          <t>298790</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3283,7 +3283,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>414637</t>
+          <t>452128</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3303,7 +3303,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>686477</t>
+          <t>750917</t>
         </is>
       </c>
     </row>
@@ -3316,62 +3316,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>194932; 205571</t>
+          <t>194875; 205495</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>238361; 247820</t>
+          <t>238785; 247849</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>244854; 254595</t>
+          <t>245104; 254475</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>265833; 275925</t>
+          <t>291414; 303042</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>322559; 332719</t>
+          <t>322506; 332737</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>368763; 384589</t>
+          <t>368547; 383796</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>389976; 397694</t>
+          <t>388617; 397691</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>408935; 418780</t>
+          <t>445573; 456426</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>521739; 536567</t>
+          <t>520981; 536714</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>612947; 630572</t>
+          <t>612674; 630509</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>637596; 650668</t>
+          <t>637024; 650104</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>678549; 693163</t>
+          <t>742341; 756751</t>
         </is>
       </c>
     </row>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3340866</t>
+          <t>3398193</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3491,7 +3491,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>3553187</t>
+          <t>3619216</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>6894053</t>
+          <t>7017410</t>
         </is>
       </c>
     </row>
@@ -3524,62 +3524,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>3107381; 3153465</t>
+          <t>3106908; 3151417</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>3235833; 3289280</t>
+          <t>3235543; 3289252</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>3197578; 3248907</t>
+          <t>3200247; 3250951</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>3313369; 3370348</t>
+          <t>3369388; 3420935</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>3197097; 3246151</t>
+          <t>3198295; 3247317</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>3401818; 3453496</t>
+          <t>3401162; 3450549</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>3388285; 3433545</t>
+          <t>3391242; 3434231</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>3532799; 3573450</t>
+          <t>3599760; 3635232</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>6315493; 6383131</t>
+          <t>6317930; 6390272</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>6654781; 6728209</t>
+          <t>6654579; 6727068</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>6606123; 6671010</t>
+          <t>6607416; 6672500</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>6861345; 6933410</t>
+          <t>6983679; 7046356</t>
         </is>
       </c>
     </row>
